--- a/test_data/WTA/WTA Pillar2 CountryCommentary/WTA Pillar2 CountryCommentary_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 CountryCommentary/WTA Pillar2 CountryCommentary_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -40,11 +40,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="001F4E78"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
@@ -65,7 +60,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -74,9 +69,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -444,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K4"/>
+  <dimension ref="A1:K5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -561,17 +553,17 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>Country Commentary did not show the expected placeholder.</t>
+          <t>Country Commentary loaded with the placeholder visible.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>[FAIL] Placeholder instruction text is visible</t>
+          <t>[PASS] Placeholder instruction text is visible</t>
         </is>
       </c>
       <c r="K2" s="3" t="inlineStr">
         <is>
-          <t>FAIL</t>
+          <t>PASS</t>
         </is>
       </c>
     </row>
@@ -628,7 +620,7 @@
           <t>[PASS] Commentary heading, Export control and first section are visible</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="K3" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
@@ -687,7 +679,67 @@
           <t>[PASS] 'No countries found' message is shown for a non-existent search term</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="K4" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>P2CC_04</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 CountryCommentary</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>The 'Export:' control downloads a real, non-empty commentary PDF</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Export commentary as PDF' button must trigger a real download with no failure and a non-zero size - P2CC_02 only proved the 'Export:' label is visible, not that the export button actually produces a file.</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on Country Commentary.</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Country Commentary
+2. Select Australia
+3. Click the 'Export commentary as PDF' button
+4. Verify a real, non-empty PDF download completed</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the 'Export commentary as PDF' button must trigger a real download with no failure and a non-zero size - P2CC_02 only proved the 'Export:' label is visible, not that the export button actually produces a file.</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Commentary export downloaded 'AU_Australia_Commentary.pdf' (20967 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Exporting the commentary downloads a real, non-empty .pdf file with no failure</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 CountryCommentary/WTA Pillar2 CountryCommentary_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 CountryCommentary/WTA Pillar2 CountryCommentary_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K5"/>
+  <dimension ref="A1:K2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +512,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2CC_01</t>
+          <t>P2CC_03</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,224 +522,47 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Country Commentary loads with the jurisdiction placeholder</t>
+          <t>Country search shows a 'no match' message for a bogus name</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>The page must load showing the left-panel instruction text.</t>
+          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>User is logged in.</t>
+          <t>User is logged in and on Country Commentary.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>-</t>
+          <t>Search term: zzzznotarealcountry</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Pillar 2 &gt; Country Commentary
-2. Verify the placeholder text is visible</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>The page must load showing the left-panel instruction text.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Country Commentary loaded with the placeholder visible.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Placeholder instruction text is visible</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>P2CC_02</t>
-        </is>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 CountryCommentary</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting a jurisdiction renders its commentary</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' must render 'Commentary on Australia, last updated ...' with an 'Export:' control and an 'A. Legislative Framework' section.</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Country Commentary.</t>
-        </is>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Country Commentary
-2. Check 'Australia'
-3. Verify the commentary heading, Export control and first section are visible</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="inlineStr">
-        <is>
-          <t>Checking 'Australia' must render 'Commentary on Australia, last updated ...' with an 'Export:' control and an 'A. Legislative Framework' section.</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>Selecting Australia rendered its country commentary with the Export control and the 'A. Legislative Framework' section.</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Commentary heading, Export control and first section are visible</t>
-        </is>
-      </c>
-      <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>P2CC_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 CountryCommentary</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Country search shows a 'no match' message for a bogus name</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on Country Commentary.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Search term: zzzznotarealcountry</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Country Commentary
 2. Search for 'zzzznotarealcountry'
 3. Verify the 'No countries found' message is shown</t>
         </is>
       </c>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="H2" s="2" t="inlineStr">
         <is>
           <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
         </is>
       </c>
-      <c r="I4" s="2" t="inlineStr">
+      <c r="I2" s="2" t="inlineStr">
         <is>
           <t>Searching for a bogus country name correctly showed the 'No countries found' message.</t>
         </is>
       </c>
-      <c r="J4" s="2" t="inlineStr">
+      <c r="J2" s="2" t="inlineStr">
         <is>
           <t>[PASS] 'No countries found' message is shown for a non-existent search term</t>
         </is>
       </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>P2CC_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>WTA Pillar2 CountryCommentary</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>The 'Export:' control downloads a real, non-empty commentary PDF</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the 'Export commentary as PDF' button must trigger a real download with no failure and a non-zero size - P2CC_02 only proved the 'Export:' label is visible, not that the export button actually produces a file.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on Country Commentary.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open Country Commentary
-2. Select Australia
-3. Click the 'Export commentary as PDF' button
-4. Verify a real, non-empty PDF download completed</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the 'Export commentary as PDF' button must trigger a real download with no failure and a non-zero size - P2CC_02 only proved the 'Export:' label is visible, not that the export button actually produces a file.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Commentary export downloaded 'AU_Australia_Commentary.pdf' (20967 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Exporting the commentary downloads a real, non-empty .pdf file with no failure</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>

--- a/test_data/WTA/WTA Pillar2 CountryCommentary/WTA Pillar2 CountryCommentary_Test_Cases.xlsx
+++ b/test_data/WTA/WTA Pillar2 CountryCommentary/WTA Pillar2 CountryCommentary_Test_Cases.xlsx
@@ -30,7 +30,7 @@
       <color rgb="00FFFFFF"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="5">
     <fill>
       <patternFill/>
     </fill>
@@ -47,6 +47,11 @@
         <fgColor rgb="00C6EFCE"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -60,7 +65,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
@@ -69,6 +74,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -436,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -512,7 +520,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>P2CC_03</t>
+          <t>P2CC_01</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -522,49 +530,107 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>Country search shows a 'no match' message for a bogus name</t>
+          <t>Country Commentary loads with the jurisdiction placeholder</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
+          <t>The page must load showing the left-panel instruction text.</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
+          <t>User is logged in.</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open Pillar 2 &gt; Country Commentary
+2. Verify the placeholder text is visible</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>The page must load showing the left-panel instruction text.</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>Country Commentary loaded with the placeholder visible.</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Placeholder instruction text is visible</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>P2CC_02</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>WTA Pillar2 CountryCommentary</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a jurisdiction renders its commentary</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' must render 'Commentary on Australia, last updated ...' with an 'Export:' control and an 'A. Legislative Framework' section.</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
           <t>User is logged in and on Country Commentary.</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>Search term: zzzznotarealcountry</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
         <is>
           <t>1. Log in and open Country Commentary
-2. Search for 'zzzznotarealcountry'
-3. Verify the 'No countries found' message is shown</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country name must show 'No countries found matching...'.</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a bogus country name correctly showed the 'No countries found' message.</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No countries found' message is shown for a non-existent search term</t>
-        </is>
-      </c>
-      <c r="K2" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
+2. Check 'Australia'
+3. Verify the commentary heading, Export control and first section are visible</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Checking 'Australia' must render 'Commentary on Australia, last updated ...' with an 'Export:' control and an 'A. Legislative Framework' section.</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Selecting a jurisdiction did not render the expected commentary content.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>[FAIL] Commentary heading, Export control and first section are visible</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
+          <t>FAIL</t>
         </is>
       </c>
     </row>
